--- a/conformance/fixtures/003-list-sheet-filter/template.xlsx
+++ b/conformance/fixtures/003-list-sheet-filter/template.xlsx
@@ -27,7 +27,7 @@
     <t>Data</t>
   </si>
   <si>
-    <t>header_row</t>
+    <t>source_table</t>
   </si>
   <si>
     <t>1</t>
@@ -471,7 +471,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -503,7 +503,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -524,6 +524,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/conformance/fixtures/003-list-sheet-filter/template.xlsx
+++ b/conformance/fixtures/003-list-sheet-filter/template.xlsx
@@ -4,16 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
     <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="_Allowed" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="__lists__" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>name</t>
   </si>
@@ -45,13 +45,16 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>{{ @filter [Customer] in _Allowed }}</t>
+    <t>{{ @filter [Customer] in __lists__[Allowed] }}</t>
   </si>
   <si>
     <t>{{ [Customer] }}</t>
   </si>
   <si>
     <t>{{ [Amount] }}</t>
+  </si>
+  <si>
+    <t>Allowed</t>
   </si>
   <si>
     <t>Acme</t>
@@ -471,7 +474,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -503,13 +506,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -522,8 +525,13 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>